--- a/data/trans_dic/IP1003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen Alergias crónicas</t>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,83</t>
+          <t>0,49; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,7</t>
+          <t>0,42; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,59</t>
+          <t>1,08; 6,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,8</t>
+          <t>0,45; 4,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,52</t>
+          <t>1,18; 4,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,23</t>
+          <t>0,23; 2,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,61</t>
+          <t>0,47; 2,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,32</t>
+          <t>4,26; 9,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,69</t>
+          <t>2,37; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,01</t>
+          <t>1,64; 6,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,54</t>
+          <t>1,59; 6,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,37</t>
+          <t>3,82; 8,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,7</t>
+          <t>3,86; 8,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,45</t>
+          <t>2,95; 7,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,43</t>
+          <t>2,82; 9,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,03</t>
+          <t>4,54; 7,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,1</t>
+          <t>3,6; 6,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,8</t>
+          <t>2,78; 6,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,49</t>
+          <t>2,78; 7,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,59</t>
+          <t>5,13; 13,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,63</t>
+          <t>3,67; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,44</t>
+          <t>4,28; 10,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,51</t>
+          <t>3,55; 9,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,52</t>
+          <t>5,6; 13,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 13,94</t>
+          <t>5,97; 13,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,32</t>
+          <t>4,26; 10,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 14,17</t>
+          <t>5,17; 13,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,96</t>
+          <t>6,3; 11,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,86</t>
+          <t>5,6; 10,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,52</t>
+          <t>4,99; 9,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,25</t>
+          <t>5,0; 10,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,21</t>
+          <t>3,56; 8,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,37</t>
+          <t>4,6; 11,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,05</t>
+          <t>3,03; 8,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,6</t>
+          <t>4,75; 10,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 12,6</t>
+          <t>6,22; 12,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,07</t>
+          <t>4,54; 11,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,23</t>
+          <t>4,38; 11,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 15,35</t>
+          <t>8,09; 15,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,84</t>
+          <t>5,66; 9,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,87</t>
+          <t>5,26; 10,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,74</t>
+          <t>4,4; 9,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,07</t>
+          <t>7,29; 12,13</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,46</t>
+          <t>4,71; 7,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,18</t>
+          <t>3,43; 6,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,08</t>
+          <t>3,39; 6,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,18</t>
+          <t>4,0; 7,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,44</t>
+          <t>5,56; 8,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,7</t>
+          <t>4,64; 7,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,7</t>
+          <t>3,92; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,45</t>
+          <t>6,47; 10,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,61</t>
+          <t>5,47; 7,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,52</t>
+          <t>4,53; 6,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,92</t>
+          <t>4,04; 5,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,2</t>
+          <t>5,81; 8,36</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2793</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3091</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>519; 5038</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>557; 5309</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1308; 8079</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>647; 5790</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4568</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3089</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2689; 10651</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>665; 6917</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1211; 6832</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3467</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16431</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9644</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5466</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14949</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15907</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12185</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9310</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>31381</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25551</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19195</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14776</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10797; 23526</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5545; 16714</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3450; 12875</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10890</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9694; 21959</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10302; 23369</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7602; 19263</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5129; 16821</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>23035; 40475</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18031; 34303</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13044; 28189</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9461; 23899</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10982</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9869</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10451</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12476</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14740</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12521</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18157</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23458</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24609</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26239</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>28608</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6543; 16813</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5689; 15933</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8080; 20118</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6137; 16821</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7922; 18734</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9473; 21657</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8039; 20012</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10924; 28325</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16961; 31793</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17545; 34193</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18826; 36363</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>19209; 40837</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9616</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18954</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12592</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34572</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>30336</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25904</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22208</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>54944</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6910; 17002</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7875; 19462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5243; 15358</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>13094; 29504</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12812; 25850</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8075; 19955</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7618; 19656</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>24706; 47123</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>22629; 39179</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18368; 35241</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15286; 31326</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>42364; 70447</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33189</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32132</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36603</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>62635</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>90606</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>78857</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>32109; 51320</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24255; 43089</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23846; 43540</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26562; 47281</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>40194; 61202</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34688; 57298</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29223; 50166</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>49192; 80052</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>76829; 107294</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>65827; 94505</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>58482; 86083</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>82784; 119073</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,75</t>
+          <t>0,49; 4,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,03</t>
+          <t>0,43; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,66</t>
+          <t>1,17; 6,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,01</t>
+          <t>0,45; 3,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,68</t>
+          <t>1,08; 4,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,38</t>
+          <t>0,25; 2,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,67</t>
+          <t>0,47; 2,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,29</t>
+          <t>4,27; 9,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,15</t>
+          <t>2,16; 6,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,12</t>
+          <t>1,82; 5,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,87</t>
+          <t>1,69; 6,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,65</t>
+          <t>3,92; 8,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,75</t>
+          <t>3,89; 8,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,46</t>
+          <t>2,93; 7,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,25</t>
+          <t>2,72; 9,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,98</t>
+          <t>4,51; 8,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,85</t>
+          <t>3,72; 7,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,02</t>
+          <t>2,73; 5,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,02</t>
+          <t>2,83; 7,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,18</t>
+          <t>5,23; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,29</t>
+          <t>3,7; 10,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,65</t>
+          <t>4,63; 10,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,72</t>
+          <t>3,31; 9,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,24</t>
+          <t>5,37; 13,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 13,66</t>
+          <t>5,69; 13,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,61</t>
+          <t>3,88; 10,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,39</t>
+          <t>5,03; 13,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,82</t>
+          <t>6,45; 11,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,91</t>
+          <t>5,62; 10,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,63</t>
+          <t>5,01; 9,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,62</t>
+          <t>5,2; 10,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,76</t>
+          <t>3,55; 9,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,36</t>
+          <t>4,64; 11,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,86</t>
+          <t>3,35; 8,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,71</t>
+          <t>4,86; 10,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,55</t>
+          <t>6,61; 13,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,21</t>
+          <t>4,57; 11,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,29</t>
+          <t>4,47; 11,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 15,43</t>
+          <t>8,25; 15,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,79</t>
+          <t>5,58; 9,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,09</t>
+          <t>5,17; 10,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,02</t>
+          <t>4,32; 8,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,13</t>
+          <t>7,21; 11,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,54</t>
+          <t>4,53; 7,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,53; 6,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,18</t>
+          <t>3,35; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,12</t>
+          <t>4,13; 7,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,47</t>
+          <t>5,42; 8,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,66</t>
+          <t>4,68; 7,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,74</t>
+          <t>3,98; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,53</t>
+          <t>6,48; 10,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,64</t>
+          <t>5,52; 7,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,5</t>
+          <t>4,51; 6,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,94</t>
+          <t>3,97; 5,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,36</t>
+          <t>5,56; 8,33</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>519; 5038</t>
+          <t>519; 5081</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 3691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>557; 5309</t>
+          <t>565; 4850</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1719</t>
+          <t>0; 1792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1308; 8079</t>
+          <t>1416; 8434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>647; 5790</t>
+          <t>649; 5394</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 5122</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3089</t>
+          <t>0; 3825</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2689; 10651</t>
+          <t>2455; 9850</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>665; 6917</t>
+          <t>734; 6607</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1211; 6832</t>
+          <t>1209; 7155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>0; 3114</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10797; 23526</t>
+          <t>10822; 23504</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5545; 16714</t>
+          <t>5060; 16013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3450; 12875</t>
+          <t>3827; 12463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2517; 10890</t>
+          <t>2680; 10419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9694; 21959</t>
+          <t>9949; 22434</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10302; 23369</t>
+          <t>10385; 23609</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7602; 19263</t>
+          <t>7553; 18929</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5129; 16821</t>
+          <t>4936; 16389</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23035; 40475</t>
+          <t>22876; 41221</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18031; 34303</t>
+          <t>18648; 35062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13044; 28189</t>
+          <t>12776; 27924</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9461; 23899</t>
+          <t>9642; 24157</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6543; 16813</t>
+          <t>6673; 17027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5689; 15933</t>
+          <t>5722; 15878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8080; 20118</t>
+          <t>8739; 20581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6137; 16821</t>
+          <t>5730; 16582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7922; 18734</t>
+          <t>7600; 18556</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9473; 21657</t>
+          <t>9018; 21969</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8039; 20012</t>
+          <t>7312; 18896</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10924; 28325</t>
+          <t>10636; 28642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16961; 31793</t>
+          <t>17352; 31927</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17545; 34193</t>
+          <t>17628; 33700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18826; 36363</t>
+          <t>18898; 36436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19209; 40837</t>
+          <t>19992; 40133</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6910; 17002</t>
+          <t>6892; 17779</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7875; 19462</t>
+          <t>7945; 19643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5243; 15358</t>
+          <t>5800; 15398</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13094; 29504</t>
+          <t>13395; 29756</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12812; 25850</t>
+          <t>13621; 27595</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8075; 19955</t>
+          <t>8129; 19767</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7618; 19656</t>
+          <t>7788; 19531</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24706; 47123</t>
+          <t>25193; 47843</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22629; 39179</t>
+          <t>22329; 39192</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18368; 35241</t>
+          <t>18070; 35170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15286; 31326</t>
+          <t>15001; 30538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42364; 70447</t>
+          <t>41892; 69528</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32109; 51320</t>
+          <t>30846; 51436</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24255; 43089</t>
+          <t>24901; 44335</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23846; 43540</t>
+          <t>23611; 41695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26562; 47281</t>
+          <t>27416; 50068</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40194; 61202</t>
+          <t>39158; 60760</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34688; 57298</t>
+          <t>35045; 56959</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29223; 50166</t>
+          <t>29652; 50237</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49192; 80052</t>
+          <t>49293; 79927</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76829; 107294</t>
+          <t>77445; 107716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65827; 94505</t>
+          <t>65552; 95580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58482; 86083</t>
+          <t>57546; 85532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82784; 119073</t>
+          <t>79215; 118587</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1003-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -717,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,79</t>
+          <t>1,1; 6,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,45; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,68</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,95</t>
+          <t>0,49; 4,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,73</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,43; 3,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,33</t>
+          <t>1,14; 4,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,27</t>
+          <t>0,25; 2,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,8</t>
+          <t>0,44; 2,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,28</t>
+          <t>3,85; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,85</t>
+          <t>3,92; 8,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,92</t>
+          <t>2,96; 7,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,57</t>
+          <t>2,39; 7,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,84</t>
+          <t>4,25; 9,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,84</t>
+          <t>2,3; 6,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,34</t>
+          <t>1,79; 6,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,02</t>
+          <t>1,71; 7,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,13</t>
+          <t>4,45; 8,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,0</t>
+          <t>3,71; 7,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,96</t>
+          <t>2,78; 5,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,1</t>
+          <t>2,41; 5,9</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,61%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,35</t>
+          <t>5,66; 13,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,25</t>
+          <t>6,08; 13,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,9</t>
+          <t>3,78; 10,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,58</t>
+          <t>4,97; 13,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 13,11</t>
+          <t>5,5; 13,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 13,85</t>
+          <t>3,74; 10,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,02</t>
+          <t>4,62; 11,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,54</t>
+          <t>3,86; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,87</t>
+          <t>6,3; 11,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,75</t>
+          <t>5,54; 10,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,65</t>
+          <t>5,06; 9,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,44</t>
+          <t>5,01; 10,1</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,55%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,16</t>
+          <t>6,08; 12,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,46</t>
+          <t>4,5; 11,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,89</t>
+          <t>4,39; 11,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,8</t>
+          <t>8,66; 16,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,39</t>
+          <t>3,61; 9,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,11</t>
+          <t>4,56; 11,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,22</t>
+          <t>3,36; 9,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 15,66</t>
+          <t>5,55; 11,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,79</t>
+          <t>5,51; 9,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,07</t>
+          <t>5,19; 9,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,79</t>
+          <t>4,42; 8,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,97</t>
+          <t>7,78; 12,81</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,55</t>
+          <t>5,43; 8,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,28</t>
+          <t>4,81; 7,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,92</t>
+          <t>3,92; 6,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,54</t>
+          <t>6,49; 10,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,41</t>
+          <t>4,59; 7,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,61</t>
+          <t>3,45; 6,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,74</t>
+          <t>3,29; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,51</t>
+          <t>4,66; 8,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,67</t>
+          <t>5,46; 7,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,57</t>
+          <t>4,48; 6,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,9</t>
+          <t>4,01; 5,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,33</t>
+          <t>6,01; 8,58</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1844</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3587</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>252</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>746</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>519; 5081</t>
+          <t>1340; 7999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>647; 5493</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>565; 4850</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1792</t>
+          <t>0; 2400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1416; 8434</t>
+          <t>519; 5127</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>649; 5394</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>566; 4870</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3825</t>
+          <t>0; 1413</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2455; 9850</t>
+          <t>2584; 10285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>734; 6607</t>
+          <t>736; 6485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1209; 7155</t>
+          <t>1138; 6673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3114</t>
+          <t>0; 2679</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14949</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16431</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9644</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7010</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5466</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14949</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15907</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12185</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>12248</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10822; 23504</t>
+          <t>9758; 21232</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5060; 16013</t>
+          <t>10467; 23235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3827; 12463</t>
+          <t>7640; 19231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2680; 10419</t>
+          <t>3755; 11480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9949; 22434</t>
+          <t>10767; 23607</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10385; 23609</t>
+          <t>5387; 15641</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7553; 18929</t>
+          <t>3774; 12655</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4936; 16389</t>
+          <t>2475; 10679</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22876; 41221</t>
+          <t>22540; 40701</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18648; 35062</t>
+          <t>18605; 35550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12776; 27924</t>
+          <t>13014; 27184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9642; 24157</t>
+          <t>7275; 17804</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12476</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12521</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10982</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9869</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>13718</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12476</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14740</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>27577</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6673; 17027</t>
+          <t>8016; 19134</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5722; 15878</t>
+          <t>9635; 22105</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8739; 20581</t>
+          <t>7129; 19467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5730; 16582</t>
+          <t>9904; 26291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7600; 18556</t>
+          <t>7020; 17338</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9018; 21969</t>
+          <t>5785; 16460</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7312; 18896</t>
+          <t>8722; 21608</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10636; 28642</t>
+          <t>6737; 17549</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17352; 31927</t>
+          <t>16941; 32192</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17628; 33700</t>
+          <t>17365; 34035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18898; 36436</t>
+          <t>19102; 35932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19992; 40133</t>
+          <t>18728; 37768</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18954</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12592</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34849</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11382</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12942</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9616</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20372</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18954</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12962</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12592</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>56027</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6892; 17779</t>
+          <t>12532; 25958</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7945; 19643</t>
+          <t>8000; 19694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5800; 15398</t>
+          <t>7639; 19542</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13395; 29756</t>
+          <t>25343; 46925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13621; 27595</t>
+          <t>7000; 17873</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8129; 19767</t>
+          <t>7817; 19483</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7788; 19531</t>
+          <t>5820; 15690</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25193; 47843</t>
+          <t>14235; 29842</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22329; 39192</t>
+          <t>22051; 39359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18070; 35170</t>
+          <t>18118; 34471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15001; 30538</t>
+          <t>15353; 30368</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41892; 69528</t>
+          <t>42753; 70340</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30846; 51436</t>
+          <t>39235; 60973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24901; 44335</t>
+          <t>35965; 57637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23611; 41695</t>
+          <t>29165; 49869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27416; 50068</t>
+          <t>45376; 72397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>39158; 60760</t>
+          <t>31291; 50830</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35045; 56959</t>
+          <t>24394; 43668</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29652; 50237</t>
+          <t>23158; 42850</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49293; 79927</t>
+          <t>29234; 50580</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77445; 107716</t>
+          <t>76611; 106770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65552; 95580</t>
+          <t>65194; 94771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57546; 85532</t>
+          <t>58078; 85840</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79215; 118587</t>
+          <t>79789; 113760</t>
         </is>
       </c>
     </row>
